--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260729.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>11,600,000</t>
+          <t>11,760,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.91%</t>
+          <t>17.07%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>5.14%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.77%</t>
         </is>
       </c>
     </row>
@@ -682,73 +682,73 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>7,600,000</t>
+          <t>1,730,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>40,000,000</t>
+          <t>7,600,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,730,000</t>
+          <t>40,000,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>6,400,000</t>
+          <t>990,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>6,400,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>931,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -990,24 +990,24 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>880,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,198 +1019,198 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>825,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>124,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10,700,000</t>
+          <t>1,750,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>124,500</t>
+          <t>760,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>760,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1227,34 +1227,34 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>7,498,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1271,34 +1271,34 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>149,000</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>4,587,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>1,604,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1437,88 +1437,88 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>834,000</t>
+          <t>110,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>624,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,574,084,004</t>
+          <t>19,713,472,017</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-819,390,819</t>
+          <t>907,505,289</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
